--- a/results/tables/04_community_composition_measures/table2_species_pc_pollution_regression.xlsx
+++ b/results/tables/04_community_composition_measures/table2_species_pc_pollution_regression.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.6</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0751</v>
+        <v>0.0042</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0634</v>
+        <v>-0.003</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0314</v>
+        <v>-0.233</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.53</v>
+        <v>-0.76</v>
       </c>
       <c r="H2" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13.6</v>
+        <v>17.8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0667</v>
+        <v>0.0109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0549</v>
+        <v>0.0038</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0225</v>
+        <v>-0.3568</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="H3" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4">
@@ -536,22 +536,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.5</v>
+        <v>13.8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.059</v>
+        <v>0.0406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0471</v>
+        <v>0.0337</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0186</v>
+        <v>0.6192</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.23</v>
+        <v>2.43</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.0905</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0127</v>
+        <v>0.0839</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002</v>
+        <v>-0.7257</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>-3.72</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0287</v>
+        <v>0.0427</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0164</v>
+        <v>0.0358</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0106</v>
+        <v>-0.4324</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.53</v>
+        <v>-2.49</v>
       </c>
       <c r="H6" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
@@ -620,50 +620,50 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0005</v>
+        <v>0.0027</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0122</v>
+        <v>-0.0045</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0013</v>
+        <v>0.1044</v>
       </c>
       <c r="G7" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="H7" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PC1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PC7</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0186</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.0062</v>
+        <v>-0.0111</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.008</v>
+        <v>-0.0495</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.22</v>
+        <v>-0.04</v>
       </c>
       <c r="H8" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -672,26 +672,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.7</v>
+        <v>15.4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1062</v>
+        <v>0.0419</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0636</v>
+        <v>0.0313</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0638</v>
+        <v>-1.1313</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.58</v>
+        <v>-1.98</v>
       </c>
       <c r="H9" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -700,26 +700,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0054</v>
+        <v>0.0289</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.042</v>
+        <v>0.0181</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0124</v>
+        <v>-0.6458</v>
       </c>
       <c r="G10" t="n">
-        <v>0.34</v>
+        <v>-1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -728,82 +728,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.4</v>
+        <v>6.8</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1456</v>
+        <v>0.028</v>
       </c>
       <c r="E11" t="n">
-        <v>0.105</v>
+        <v>0.0172</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0603</v>
+        <v>0.7569</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.89</v>
+        <v>1.61</v>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PC4</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.0271</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.0197</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="H12" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.0411</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.008800000000000001</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="H13" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
